--- a/results_all_data/summary_cut_off_values0.95.xlsx
+++ b/results_all_data/summary_cut_off_values0.95.xlsx
@@ -1,74 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbere\Documents\GitHub\multiresistance_networks2\results_all_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B02B819-7AB0-44EA-B85E-687ED645168C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2865" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>dataset</t>
-  </si>
-  <si>
-    <t>cut_off_eSup</t>
-  </si>
-  <si>
-    <t>cut_off_cLift</t>
-  </si>
-  <si>
-    <t>2018_BLSE</t>
-  </si>
-  <si>
-    <t>2019_BLSE</t>
-  </si>
-  <si>
-    <t>2020_BLSE</t>
-  </si>
-  <si>
-    <t>2021_BLSE</t>
-  </si>
-  <si>
-    <t>2022_BLSE</t>
-  </si>
-  <si>
-    <t>2018_non_BLSE</t>
-  </si>
-  <si>
-    <t>2019_non_BLSE</t>
-  </si>
-  <si>
-    <t>2020_non_BLSE</t>
-  </si>
-  <si>
-    <t>2021_non_BLSE</t>
-  </si>
-  <si>
-    <t>2022_non_BLSE</t>
+    <t xml:space="preserve">dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cut_off_eSup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cut_off_cLift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022_non_BLSE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -97,23 +87,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -395,11 +375,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -410,118 +390,118 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.25684965823323003</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1.0764886819714801</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" t="n">
+        <v>0.25414751030003</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.07782091899034</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.23618755767139801</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.06992477471224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="n">
+        <v>0.230766729670547</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.07071814122642</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.24150391529863499</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1.07347261628409</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="n">
+        <v>0.240019090676393</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.07411515062001</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
-        <v>0.26174149022226301</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1.0648479858903199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="n">
+        <v>0.264371694798482</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.06529576203788</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1">
-        <v>0.27092902359811399</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.0584159873249199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="n">
+        <v>0.26881940189338</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.06060676621046</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>2.98726159622285E-2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.0560938364655501</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" t="n">
+        <v>0.0299512066397042</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0568306656008</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
-        <v>2.9298832319824501E-2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.05135155707674</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" t="n">
+        <v>0.0283465949421292</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.05086755337803</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1">
-        <v>2.9985532174205302E-2</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.0522074002789901</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" t="n">
+        <v>0.0293249230480402</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.05161629144824</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1">
-        <v>3.09161849770767E-2</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1.04500410034266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B10" t="n">
+        <v>0.0256304731373951</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.04466018770418</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1">
-        <v>3.3714657592765401E-2</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1.0412183869963501</v>
+      <c r="B11" t="n">
+        <v>0.033180662805341</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.04015998742536</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>